--- a/defaults/taxonomy.xlsx
+++ b/defaults/taxonomy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dltkd\Desktop\261004 BEOL AX day2\defaults\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36F9D17-4B8E-493B-91C2-47AEF9F2BFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7FCF8B-C281-4433-8222-99579D8A89BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{4839889B-8E27-4F13-89D4-7E9141DB71F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" activeTab="1" xr2:uid="{4839889B-8E27-4F13-89D4-7E9141DB71F6}"/>
   </bookViews>
   <sheets>
     <sheet name="taxonomy" sheetId="1" r:id="rId1"/>
@@ -521,9 +521,6 @@
     <t>Q-COM-001</t>
   </si>
   <si>
-    <t>이 chunk에 아직 해결되지 않은 위험(추가 확인이 필요한 불량, 미검증 조건, 후속 평가 필요)이 명시되어 있는가.</t>
-  </si>
-  <si>
     <t>공통</t>
   </si>
   <si>
@@ -617,6 +614,10 @@
   </si>
   <si>
     <t>SF2X, 2나노4세대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 chunk가 BEOL interconnect 공정에 관련한 내용이 맞는가?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1275,7 +1276,7 @@
         <v>48</v>
       </c>
       <c r="H19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1298,7 +1299,7 @@
         <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
@@ -1306,10 +1307,10 @@
         <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
@@ -1317,10 +1318,10 @@
         <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
@@ -1328,10 +1329,10 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
@@ -1339,10 +1340,10 @@
         <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
@@ -1350,10 +1351,10 @@
         <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
@@ -1949,6 +1950,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE934B5B-8991-47BA-BE0F-83BE9B58593F}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="11.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="99.9140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -1969,10 +1974,10 @@
         <v>158</v>
       </c>
       <c r="B2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" t="s">
         <v>159</v>
-      </c>
-      <c r="C2" t="s">
-        <v>160</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1991,13 +1996,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" t="s">
         <v>161</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>162</v>
-      </c>
-      <c r="C1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
@@ -2008,7 +2013,7 @@
         <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -2019,7 +2024,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -2030,7 +2035,7 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -2041,84 +2046,84 @@
         <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" t="s">
         <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
         <v>130</v>
       </c>
       <c r="C7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B8" t="s">
         <v>130</v>
       </c>
       <c r="C8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -2129,7 +2134,7 @@
         <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
@@ -2140,7 +2145,7 @@
         <v>115</v>
       </c>
       <c r="C14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2159,13 +2164,13 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" t="s">
         <v>173</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>174</v>
-      </c>
-      <c r="D1" t="s">
-        <v>175</v>
       </c>
     </row>
   </sheetData>
